--- a/tests/realSuite/Piano-Viaggi_-Cadette_i_27-Febbaio-2026_con-Vettore-2/input.xlsx
+++ b/tests/realSuite/Piano-Viaggi_-Cadette_i_27-Febbaio-2026_con-Vettore-2/input.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C30"/>
+  <dimension ref="A1:C36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -531,26 +531,26 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Segonzano, Frazione Scancio, Fermata Trentino Trasporti “Snack Bar” Scancio</t>
+          <t>Giovo, Via Al Grec 2</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>IC CENTRO VALSUGANA</t>
+          <t>IC CEMBRA</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Roncegno, Fermata “Il Picchio”</t>
+          <t>Segonzano, Frazione Scancio, Fermata Trentino Trasporti “Snack Bar” Scancio</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="10">
@@ -561,7 +561,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Telve, Piazza Maggiore</t>
+          <t>Roncegno, Fermata “Il Picchio”</t>
         </is>
       </c>
       <c r="C10" t="n">
@@ -571,27 +571,27 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>IC CLES</t>
+          <t>IC CENTRO VALSUGANA</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Cles, Piazza Fiera</t>
+          <t>Telve, Piazza Maggiore</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>IC DENNO</t>
+          <t>IC CHIESE</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Denno, Piazzale scolastico degli autobus</t>
+          <t>Tione, Via Circonvallazione 44</t>
         </is>
       </c>
       <c r="C12" t="n">
@@ -601,27 +601,27 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>IC DRO</t>
+          <t>IC CLES</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Dro, Via S. Antonio 17</t>
+          <t>Cles, Piazza Fiera</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>IC FOLGARIA – LAVARONE - LUSERNA</t>
+          <t>IC DENNO</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Folgaria, fermata Palaghiaccio</t>
+          <t>Denno, Piazzale scolastico degli autobus</t>
         </is>
       </c>
       <c r="C14" t="n">
@@ -631,12 +631,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>IC LADINO DI FASSA</t>
+          <t>IC DRO</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Sen Jan, Strada Dolomites - Pozza di Fassa 67</t>
+          <t>Dro, Via S. Antonio 17</t>
         </is>
       </c>
       <c r="C15" t="n">
@@ -646,12 +646,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>IC LAVIS</t>
+          <t>IC FOLGARIA – LAVARONE - LUSERNA</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Lavis, Via Sette 13/A</t>
+          <t>Folgaria, fermata Palaghiaccio</t>
         </is>
       </c>
       <c r="C16" t="n">
@@ -661,12 +661,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>IC MEZZOLOMBARDO PAGANELLA</t>
+          <t>IC FONDO</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Mezzolombardo, Via Degli Alpini 17</t>
+          <t>Taio, Piazza della Chiesa</t>
         </is>
       </c>
       <c r="C17" t="n">
@@ -676,27 +676,27 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>IC PERGINE 1</t>
+          <t>IC LADINO DI FASSA</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Pergine Valsugana, Via Caduti 39</t>
+          <t>Moena, Fermata Te Volto</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>IC PERGINE 2</t>
+          <t>IC LADINO DI FASSA</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Pergine Valsugana, Viale Dante 276 (fermata Tentazioni)</t>
+          <t>Sen Jan, Strada Dolomites - Pozza di Fassa 67</t>
         </is>
       </c>
       <c r="C19" t="n">
@@ -706,12 +706,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>IC REVO’</t>
+          <t>IC LAVIS</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Revò, Fermata del Bus ai Vigili del Fuoco</t>
+          <t>Lavis, Via Sette 13/A</t>
         </is>
       </c>
       <c r="C20" t="n">
@@ -721,12 +721,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>IC RIVA 1</t>
+          <t>IC MEZZOLOMBARDO PAGANELLA</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Riva del Garda, fermata bus vicino alla scuola D. Chiesa</t>
+          <t>Mezzolombardo, Via Degli Alpini 17</t>
         </is>
       </c>
       <c r="C21" t="n">
@@ -736,12 +736,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>IC ROVERETO EST</t>
+          <t>IC PERGINE 1</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Rovereto, Piazzale Orsi, fermata bus di fronte all’Istituto Veronesi</t>
+          <t>Pergine Valsugana, Via Caduti 39</t>
         </is>
       </c>
       <c r="C22" t="n">
@@ -751,12 +751,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>IC ROVERETO NORD</t>
+          <t>IC PERGINE 2</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Rovereto, Corso Bettini 67</t>
+          <t>Pergine Valsugana, Viale Dante 276 (fermata Tentazioni)</t>
         </is>
       </c>
       <c r="C23" t="n">
@@ -766,27 +766,27 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>IC TAIO</t>
+          <t>IC REVO’</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Taio, Piazza della Chiesa</t>
+          <t>Revò, Fermata del Bus ai Vigili del Fuoco</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>IC TIONE</t>
+          <t>IC RIVA 1</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Tione, Via Circonvallazione 44</t>
+          <t>Riva del Garda, fermata bus vicino alla scuola D. Chiesa</t>
         </is>
       </c>
       <c r="C25" t="n">
@@ -796,27 +796,27 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>IC TRENTO 6</t>
+          <t>IC ROVERETO EST</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Trento, park ex Italcementi</t>
+          <t>Rovereto, Piazzale Orsi, fermata bus di fronte all’Istituto Veronesi</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>IC VAL RENDENA</t>
+          <t>IC ROVERETO NORD</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Pinzolo, Via Collini Borciol 18</t>
+          <t>Rovereto, Corso Bettini 67</t>
         </is>
       </c>
       <c r="C27" t="n">
@@ -826,46 +826,136 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>IC VALLE DI LEDRO</t>
+          <t>IC TAIO</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Ledro, fermata bus di fronte all’IC Valle di Ledro</t>
+          <t>Taio, Piazza della Chiesa</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>IC VEZZANO</t>
+          <t>IC TIONE</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Vezzano, Via Roma 3</t>
+          <t>Tione, Via Circonvallazione 44</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
+          <t>IC TRENTO 3</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Trento, park ex Italcementi</t>
+        </is>
+      </c>
+      <c r="C30" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>IC TRENTO 6</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Trento, park ex Italcementi</t>
+        </is>
+      </c>
+      <c r="C31" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>IC VAL RENDENA</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Pinzolo, Via Collini Borciol 18</t>
+        </is>
+      </c>
+      <c r="C32" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>IC VALLE DI LEDRO</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Ledro, fermata bus di fronte all’IC Valle di Ledro</t>
+        </is>
+      </c>
+      <c r="C33" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>IC VEZZANO</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Vezzano, Via Roma 3</t>
+        </is>
+      </c>
+      <c r="C34" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
           <t>IC VIGOLO VATTARO</t>
         </is>
       </c>
-      <c r="B30" t="inlineStr">
+      <c r="B35" t="inlineStr">
         <is>
           <t>Vigolo Vattaro, Fermata bus</t>
         </is>
       </c>
-      <c r="C30" t="n">
-        <v>5</v>
+      <c r="C35" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>IS MARTINO MARTINI Students staff</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Mezzolombardo, Via Degli Alpini 17</t>
+        </is>
+      </c>
+      <c r="C36" t="n">
+        <v>15</v>
       </c>
     </row>
   </sheetData>

--- a/tests/realSuite/Piano-Viaggi_-Cadette_i_27-Febbaio-2026_con-Vettore-2/input.xlsx
+++ b/tests/realSuite/Piano-Viaggi_-Cadette_i_27-Febbaio-2026_con-Vettore-2/input.xlsx
@@ -441,7 +441,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Ala, Scuola Primaria, Via Betta 9</t>
+          <t>Scuola primaria "Abramo Betta", 9, Via Abramo Betta, Ala, Comunità della Vallagarina, Provincia di Trento, Trentino-Alto Adige/Südtirol, 38061, Italia</t>
         </is>
       </c>
       <c r="C2" t="n">

--- a/tests/realSuite/Piano-Viaggi_-Cadette_i_27-Febbaio-2026_con-Vettore-2/input.xlsx
+++ b/tests/realSuite/Piano-Viaggi_-Cadette_i_27-Febbaio-2026_con-Vettore-2/input.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C36"/>
+  <dimension ref="A1:C34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -451,12 +451,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>IC ALDENO MATTARELLO</t>
+          <t>IC ARCO GARDA SCUOLA</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Trento, fermata bus sopra al parco di Via Torre Franca</t>
+          <t>Scuole superiori Gardascuola, 1, Via Ventiquattro Maggio, Caneve, Chiarano, Arco, Comunità Alto Garda e Ledro, Provincia di Trento, Trentino-Alto Adige/Südtirol, 38062, Italia</t>
         </is>
       </c>
       <c r="C3" t="n">
@@ -466,12 +466,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>IC ARCO GARDA SCUOLA</t>
+          <t>IC BASSA VAL DI SOLE</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Arco, stazione delle corriere</t>
+          <t>Malè, Stazione Nuova di Malè</t>
         </is>
       </c>
       <c r="C4" t="n">
@@ -481,117 +481,117 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>IC AVIO</t>
+          <t>IC CAVALESE</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Avio, Viale Degasperi 69</t>
+          <t>Cavalese, Piazza Verdi 6</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>IC BASSA VAL DI SOLE</t>
+          <t>IC CEMBRA</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Malè, Stazione Nuova di Malè</t>
+          <t>Giovo, Via Al Grec 2</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>IC CAVALESE</t>
+          <t>IC CEMBRA</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Cavalese, Piazza Verdi 6</t>
+          <t>Segonzano, Frazione Scancio, Fermata Trentino Trasporti “Snack Bar” Scancio</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>IC CEMBRA</t>
+          <t>IC CENTRO VALSUGANA</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Giovo, Via Al Grec 2</t>
+          <t>Roncegno, Fermata “Il Picchio”</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>IC CEMBRA</t>
+          <t>IC CENTRO VALSUGANA</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Segonzano, Frazione Scancio, Fermata Trentino Trasporti “Snack Bar” Scancio</t>
+          <t>Telve, Piazza Maggiore</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>IC CENTRO VALSUGANA</t>
+          <t>IC CHIESE</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Roncegno, Fermata “Il Picchio”</t>
+          <t>Tione, Via Circonvallazione 44</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>IC CENTRO VALSUGANA</t>
+          <t>IC CLES</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Telve, Piazza Maggiore</t>
+          <t>Cles, Piazza Fiera</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>IC CHIESE</t>
+          <t>IC DENNO</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Tione, Via Circonvallazione 44</t>
+          <t>Denno, Piazzale scolastico degli autobus</t>
         </is>
       </c>
       <c r="C12" t="n">
@@ -601,27 +601,27 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>IC CLES</t>
+          <t>IC DRO</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Cles, Piazza Fiera</t>
+          <t>Dro, Via S. Antonio 17</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>IC DENNO</t>
+          <t>IC FOLGARIA – LAVARONE - LUSERNA</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Denno, Piazzale scolastico degli autobus</t>
+          <t>Folgaria, fermata Palaghiaccio</t>
         </is>
       </c>
       <c r="C14" t="n">
@@ -631,12 +631,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>IC DRO</t>
+          <t>IC FONDO</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Dro, Via S. Antonio 17</t>
+          <t>Taio, Piazza della Chiesa</t>
         </is>
       </c>
       <c r="C15" t="n">
@@ -646,27 +646,27 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>IC FOLGARIA – LAVARONE - LUSERNA</t>
+          <t>IC LADINO DI FASSA</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Folgaria, fermata Palaghiaccio</t>
+          <t>Moena, Fermata Te Volto</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>IC FONDO</t>
+          <t>IC LADINO DI FASSA</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Taio, Piazza della Chiesa</t>
+          <t>Sen Jan, Strada Dolomites - Pozza di Fassa 67</t>
         </is>
       </c>
       <c r="C17" t="n">
@@ -676,27 +676,27 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>IC LADINO DI FASSA</t>
+          <t>IC LAVIS</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Moena, Fermata Te Volto</t>
+          <t>Lavis, Via Sette 13/A</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>IC LADINO DI FASSA</t>
+          <t>IC MEZZOLOMBARDO PAGANELLA</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Sen Jan, Strada Dolomites - Pozza di Fassa 67</t>
+          <t>Mezzolombardo, Via Degli Alpini 17</t>
         </is>
       </c>
       <c r="C19" t="n">
@@ -706,12 +706,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>IC LAVIS</t>
+          <t>IC PERGINE 1</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Lavis, Via Sette 13/A</t>
+          <t>Pergine Valsugana, Via Caduti 39</t>
         </is>
       </c>
       <c r="C20" t="n">
@@ -721,12 +721,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>IC MEZZOLOMBARDO PAGANELLA</t>
+          <t>IC PERGINE 2</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Mezzolombardo, Via Degli Alpini 17</t>
+          <t>Pergine Valsugana, Viale Dante 276 (fermata Tentazioni)</t>
         </is>
       </c>
       <c r="C21" t="n">
@@ -736,12 +736,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>IC PERGINE 1</t>
+          <t>IC REVO’</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Pergine Valsugana, Via Caduti 39</t>
+          <t>Revò, Fermata del Bus ai Vigili del Fuoco</t>
         </is>
       </c>
       <c r="C22" t="n">
@@ -751,12 +751,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>IC PERGINE 2</t>
+          <t>IC RIVA 1</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Pergine Valsugana, Viale Dante 276 (fermata Tentazioni)</t>
+          <t>Riva del Garda, fermata bus vicino alla scuola D. Chiesa</t>
         </is>
       </c>
       <c r="C23" t="n">
@@ -766,12 +766,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>IC REVO’</t>
+          <t>IC ROVERETO EST</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Revò, Fermata del Bus ai Vigili del Fuoco</t>
+          <t>Rovereto, Piazzale Orsi, fermata bus di fronte all’Istituto Veronesi</t>
         </is>
       </c>
       <c r="C24" t="n">
@@ -781,12 +781,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>IC RIVA 1</t>
+          <t>IC ROVERETO NORD</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Riva del Garda, fermata bus vicino alla scuola D. Chiesa</t>
+          <t>Rovereto, Corso Bettini 67</t>
         </is>
       </c>
       <c r="C25" t="n">
@@ -796,27 +796,27 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>IC ROVERETO EST</t>
+          <t>IC TAIO</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Rovereto, Piazzale Orsi, fermata bus di fronte all’Istituto Veronesi</t>
+          <t>Taio, Piazza della Chiesa</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>IC ROVERETO NORD</t>
+          <t>IC TIONE</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Rovereto, Corso Bettini 67</t>
+          <t>Tione, Via Circonvallazione 44</t>
         </is>
       </c>
       <c r="C27" t="n">
@@ -826,42 +826,42 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>IC TAIO</t>
+          <t>IC TRENTO 3</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Taio, Piazza della Chiesa</t>
+          <t>Trento, park ex Italcementi</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>IC TIONE</t>
+          <t>IC TRENTO 6</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Tione, Via Circonvallazione 44</t>
+          <t>Trento, park ex Italcementi</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>IC TRENTO 3</t>
+          <t>IC VAL RENDENA</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Trento, park ex Italcementi</t>
+          <t>Pinzolo, Via Collini Borciol 18</t>
         </is>
       </c>
       <c r="C30" t="n">
@@ -871,42 +871,42 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>IC TRENTO 6</t>
+          <t>IC VALLE DI LEDRO</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Trento, park ex Italcementi</t>
+          <t>Ledro, fermata bus di fronte all’IC Valle di Ledro</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>IC VAL RENDENA</t>
+          <t>IC VEZZANO</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Pinzolo, Via Collini Borciol 18</t>
+          <t>Vezzano, Via Roma 3</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>IC VALLE DI LEDRO</t>
+          <t>IC VIGOLO VATTARO</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Ledro, fermata bus di fronte all’IC Valle di Ledro</t>
+          <t>Vigolo Vattaro, Fermata bus</t>
         </is>
       </c>
       <c r="C33" t="n">
@@ -916,45 +916,15 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>IC VEZZANO</t>
+          <t>IS MARTINO MARTINI Students staff</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Vezzano, Via Roma 3</t>
+          <t>Mezzolombardo, Via Degli Alpini 17</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>IC VIGOLO VATTARO</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>Vigolo Vattaro, Fermata bus</t>
-        </is>
-      </c>
-      <c r="C35" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>IS MARTINO MARTINI Students staff</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>Mezzolombardo, Via Degli Alpini 17</t>
-        </is>
-      </c>
-      <c r="C36" t="n">
         <v>15</v>
       </c>
     </row>
